--- a/artfynd/A 7029-2026 artfynd.xlsx
+++ b/artfynd/A 7029-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16839687</v>
+        <v>135235877</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645434</v>
+        <v>645437</v>
       </c>
       <c r="R2" t="n">
-        <v>7135220</v>
+        <v>7135172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,32 +757,26 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16839689</v>
+        <v>16839687</v>
       </c>
       <c r="B3" t="n">
         <v>80432</v>
@@ -817,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645389</v>
+        <v>645434</v>
       </c>
       <c r="R3" t="n">
-        <v>7135230</v>
+        <v>7135220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,12 +860,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskog med stort lövinslag</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Klen sälg</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,6 +880,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16839689</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stektkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>645389</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7135230</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-08-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-08-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog med stort lövinslag</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Klen sälg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7029-2026 artfynd.xlsx
+++ b/artfynd/A 7029-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135235877</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16839687</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16839689</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7029-2026 artfynd.xlsx
+++ b/artfynd/A 7029-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135235877</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2026 artfynd.xlsx
+++ b/artfynd/A 7029-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135235877</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7029-2026 artfynd.xlsx
+++ b/artfynd/A 7029-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16839687</v>
+        <v>135235877</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645434</v>
+        <v>645437</v>
       </c>
       <c r="R2" t="n">
-        <v>7135220</v>
+        <v>7135172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,37 +762,31 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16839687</t>
+          <t>https://artportalen.se/Sighting/135235877</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16839689</v>
+        <v>16839687</v>
       </c>
       <c r="B3" t="n">
         <v>80432</v>
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645389</v>
+        <v>645434</v>
       </c>
       <c r="R3" t="n">
-        <v>7135230</v>
+        <v>7135220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,12 +870,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskog med stort lövinslag</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Klen sälg</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,6 +891,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16839687</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16839689</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stektkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>645389</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7135230</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-08-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-08-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog med stort lövinslag</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Klen sälg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/16839689</t>
         </is>
@@ -906,6 +1012,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
